--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G726"/>
+  <dimension ref="A1:G732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19996,6 +19996,168 @@
         </is>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D727" t="n">
+        <v>240143949</v>
+      </c>
+      <c r="E727" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="F727" t="inlineStr"/>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D728" t="n">
+        <v>172669949</v>
+      </c>
+      <c r="E728" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="D729" t="n">
+        <v>21973674</v>
+      </c>
+      <c r="E729" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="F729" t="inlineStr"/>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="D730" t="n">
+        <v>17178832</v>
+      </c>
+      <c r="E730" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="D731" t="n">
+        <v>13878355</v>
+      </c>
+      <c r="E731" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>438.4</v>
+      </c>
+      <c r="D732" t="n">
+        <v>10443687</v>
+      </c>
+      <c r="E732" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G732"/>
+  <dimension ref="A1:G738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20158,6 +20158,168 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="D733" t="n">
+        <v>169793507</v>
+      </c>
+      <c r="E733" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="F733" t="inlineStr"/>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="D734" t="n">
+        <v>161530808</v>
+      </c>
+      <c r="E734" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F734" t="inlineStr"/>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="D735" t="n">
+        <v>22082644</v>
+      </c>
+      <c r="E735" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="D736" t="n">
+        <v>16815586</v>
+      </c>
+      <c r="E736" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>435.4</v>
+      </c>
+      <c r="D737" t="n">
+        <v>10414838</v>
+      </c>
+      <c r="E737" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="D738" t="n">
+        <v>7225458</v>
+      </c>
+      <c r="E738" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G738"/>
+  <dimension ref="A1:G744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20320,6 +20320,168 @@
         </is>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="D739" t="n">
+        <v>191325722</v>
+      </c>
+      <c r="E739" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F739" t="inlineStr"/>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="D740" t="n">
+        <v>120388099</v>
+      </c>
+      <c r="E740" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="F740" t="inlineStr"/>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D741" t="n">
+        <v>31845013</v>
+      </c>
+      <c r="E741" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="D742" t="n">
+        <v>27607650</v>
+      </c>
+      <c r="E742" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>434</v>
+      </c>
+      <c r="D743" t="n">
+        <v>17647957</v>
+      </c>
+      <c r="E743" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="F743" t="inlineStr"/>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>166</v>
+      </c>
+      <c r="D744" t="n">
+        <v>6284877</v>
+      </c>
+      <c r="E744" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G744"/>
+  <dimension ref="A1:G750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20482,6 +20482,168 @@
         </is>
       </c>
     </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="D745" t="n">
+        <v>247840515</v>
+      </c>
+      <c r="E745" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="D746" t="n">
+        <v>148749413</v>
+      </c>
+      <c r="E746" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="D747" t="n">
+        <v>47472774</v>
+      </c>
+      <c r="E747" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="F747" t="inlineStr"/>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="D748" t="n">
+        <v>26257539</v>
+      </c>
+      <c r="E748" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>425.6</v>
+      </c>
+      <c r="D749" t="n">
+        <v>22333265</v>
+      </c>
+      <c r="E749" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="D750" t="n">
+        <v>6182867</v>
+      </c>
+      <c r="E750" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G750"/>
+  <dimension ref="A1:G756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20644,6 +20644,168 @@
         </is>
       </c>
     </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D751" t="n">
+        <v>255017158</v>
+      </c>
+      <c r="E751" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="D752" t="n">
+        <v>113534043</v>
+      </c>
+      <c r="E752" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F752" t="inlineStr"/>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D753" t="n">
+        <v>25982180</v>
+      </c>
+      <c r="E753" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="D754" t="n">
+        <v>21297940</v>
+      </c>
+      <c r="E754" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F754" t="inlineStr"/>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>428.4</v>
+      </c>
+      <c r="D755" t="n">
+        <v>15628479</v>
+      </c>
+      <c r="E755" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F755" t="inlineStr"/>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D756" t="n">
+        <v>9766166</v>
+      </c>
+      <c r="E756" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F756" t="inlineStr"/>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G756"/>
+  <dimension ref="A1:G762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20806,6 +20806,168 @@
         </is>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D757" t="n">
+        <v>255012158</v>
+      </c>
+      <c r="E757" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F757" t="inlineStr"/>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="D758" t="n">
+        <v>113533443</v>
+      </c>
+      <c r="E758" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D759" t="n">
+        <v>25980880</v>
+      </c>
+      <c r="E759" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F759" t="inlineStr"/>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="D760" t="n">
+        <v>21297640</v>
+      </c>
+      <c r="E760" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F760" t="inlineStr"/>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>428.4</v>
+      </c>
+      <c r="D761" t="n">
+        <v>15628379</v>
+      </c>
+      <c r="E761" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F761" t="inlineStr"/>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D762" t="n">
+        <v>9758966</v>
+      </c>
+      <c r="E762" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F762" t="inlineStr"/>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G762"/>
+  <dimension ref="A1:G768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20968,6 +20968,168 @@
         </is>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D763" t="n">
+        <v>255012158</v>
+      </c>
+      <c r="E763" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F763" t="inlineStr"/>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="D764" t="n">
+        <v>113533443</v>
+      </c>
+      <c r="E764" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F764" t="inlineStr"/>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D765" t="n">
+        <v>25980880</v>
+      </c>
+      <c r="E765" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F765" t="inlineStr"/>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="D766" t="n">
+        <v>21297640</v>
+      </c>
+      <c r="E766" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F766" t="inlineStr"/>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>428.4</v>
+      </c>
+      <c r="D767" t="n">
+        <v>15628379</v>
+      </c>
+      <c r="E767" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F767" t="inlineStr"/>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D768" t="n">
+        <v>9758966</v>
+      </c>
+      <c r="E768" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F768" t="inlineStr"/>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G768"/>
+  <dimension ref="A1:G774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21130,6 +21130,144 @@
         </is>
       </c>
     </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr"/>
+      <c r="D769" t="n">
+        <v>275738018</v>
+      </c>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr"/>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr"/>
+      <c r="D770" t="n">
+        <v>110192077</v>
+      </c>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr"/>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr"/>
+      <c r="D771" t="n">
+        <v>19795626</v>
+      </c>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr"/>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr"/>
+      <c r="D772" t="n">
+        <v>17248151</v>
+      </c>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr"/>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr"/>
+      <c r="D773" t="n">
+        <v>11364785</v>
+      </c>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr"/>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr"/>
+      <c r="D774" t="n">
+        <v>6723991</v>
+      </c>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr"/>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G774"/>
+  <dimension ref="A1:G780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21268,6 +21268,168 @@
         </is>
       </c>
     </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="D775" t="n">
+        <v>159210874</v>
+      </c>
+      <c r="E775" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="F775" t="inlineStr"/>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D776" t="n">
+        <v>77301911</v>
+      </c>
+      <c r="E776" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="F776" t="inlineStr"/>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>438.8</v>
+      </c>
+      <c r="D777" t="n">
+        <v>21791117</v>
+      </c>
+      <c r="E777" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F777" t="inlineStr"/>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="D778" t="n">
+        <v>14870839</v>
+      </c>
+      <c r="E778" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F778" t="inlineStr"/>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="D779" t="n">
+        <v>14662244</v>
+      </c>
+      <c r="E779" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="F779" t="inlineStr"/>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="D780" t="n">
+        <v>12861300</v>
+      </c>
+      <c r="E780" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="F780" t="inlineStr"/>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G780"/>
+  <dimension ref="A1:G786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21430,6 +21430,168 @@
         </is>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="D781" t="n">
+        <v>122943726</v>
+      </c>
+      <c r="E781" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F781" t="inlineStr"/>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="D782" t="n">
+        <v>74217545</v>
+      </c>
+      <c r="E782" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="F782" t="inlineStr"/>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>74.45</v>
+      </c>
+      <c r="D783" t="n">
+        <v>16747622</v>
+      </c>
+      <c r="E783" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F783" t="inlineStr"/>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>433.4</v>
+      </c>
+      <c r="D784" t="n">
+        <v>12686515</v>
+      </c>
+      <c r="E784" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="F784" t="inlineStr"/>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D785" t="n">
+        <v>9959680</v>
+      </c>
+      <c r="E785" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F785" t="inlineStr"/>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="D786" t="n">
+        <v>6193653</v>
+      </c>
+      <c r="E786" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F786" t="inlineStr"/>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G786"/>
+  <dimension ref="A1:G792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21592,6 +21592,168 @@
         </is>
       </c>
     </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="D787" t="n">
+        <v>159332847</v>
+      </c>
+      <c r="E787" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F787" t="inlineStr"/>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="D788" t="n">
+        <v>89307650</v>
+      </c>
+      <c r="E788" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="D789" t="n">
+        <v>27404755</v>
+      </c>
+      <c r="E789" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="F789" t="inlineStr"/>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="D790" t="n">
+        <v>16984343</v>
+      </c>
+      <c r="E790" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="F790" t="inlineStr"/>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>426</v>
+      </c>
+      <c r="D791" t="n">
+        <v>16185247</v>
+      </c>
+      <c r="E791" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="F791" t="inlineStr"/>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>159.8</v>
+      </c>
+      <c r="D792" t="n">
+        <v>8155068</v>
+      </c>
+      <c r="E792" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="F792" t="inlineStr"/>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G792"/>
+  <dimension ref="A1:G798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21754,6 +21754,168 @@
         </is>
       </c>
     </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="D793" t="n">
+        <v>266413782</v>
+      </c>
+      <c r="E793" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="F793" t="inlineStr"/>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D794" t="n">
+        <v>109848697</v>
+      </c>
+      <c r="E794" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D795" t="n">
+        <v>34129761</v>
+      </c>
+      <c r="E795" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>419</v>
+      </c>
+      <c r="D796" t="n">
+        <v>28796138</v>
+      </c>
+      <c r="E796" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="F796" t="inlineStr"/>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D797" t="n">
+        <v>22056501</v>
+      </c>
+      <c r="E797" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="D798" t="n">
+        <v>12240089</v>
+      </c>
+      <c r="E798" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F798" t="inlineStr"/>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G798"/>
+  <dimension ref="A1:G804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21916,6 +21916,168 @@
         </is>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="D799" t="n">
+        <v>266413782</v>
+      </c>
+      <c r="E799" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D800" t="n">
+        <v>109848697</v>
+      </c>
+      <c r="E800" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D801" t="n">
+        <v>34129761</v>
+      </c>
+      <c r="E801" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F801" t="inlineStr"/>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>419</v>
+      </c>
+      <c r="D802" t="n">
+        <v>28796138</v>
+      </c>
+      <c r="E802" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="F802" t="inlineStr"/>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D803" t="n">
+        <v>22056501</v>
+      </c>
+      <c r="E803" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="D804" t="n">
+        <v>12240089</v>
+      </c>
+      <c r="E804" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F804" t="inlineStr"/>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G804"/>
+  <dimension ref="A1:G810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22078,6 +22078,168 @@
         </is>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="D805" t="n">
+        <v>266413782</v>
+      </c>
+      <c r="E805" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D806" t="n">
+        <v>109848697</v>
+      </c>
+      <c r="E806" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D807" t="n">
+        <v>34129761</v>
+      </c>
+      <c r="E807" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>419</v>
+      </c>
+      <c r="D808" t="n">
+        <v>28796138</v>
+      </c>
+      <c r="E808" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D809" t="n">
+        <v>22056501</v>
+      </c>
+      <c r="E809" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="D810" t="n">
+        <v>12240089</v>
+      </c>
+      <c r="E810" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G810"/>
+  <dimension ref="A1:G816"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22240,6 +22240,144 @@
         </is>
       </c>
     </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr"/>
+      <c r="D811" t="n">
+        <v>137700204</v>
+      </c>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr"/>
+      <c r="D812" t="n">
+        <v>110209098</v>
+      </c>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr"/>
+      <c r="D813" t="n">
+        <v>19669433</v>
+      </c>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr"/>
+      <c r="D814" t="n">
+        <v>18568730</v>
+      </c>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr"/>
+      <c r="D815" t="n">
+        <v>17650057</v>
+      </c>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr"/>
+      <c r="D816" t="n">
+        <v>5789115</v>
+      </c>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G816"/>
+  <dimension ref="A1:G822"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22378,6 +22378,172 @@
         </is>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="D817" t="n">
+        <v>178900621</v>
+      </c>
+      <c r="E817" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D818" t="n">
+        <v>127962106</v>
+      </c>
+      <c r="E818" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>451.6</v>
+      </c>
+      <c r="D819" t="n">
+        <v>70725438</v>
+      </c>
+      <c r="E819" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D820" t="n">
+        <v>22995061</v>
+      </c>
+      <c r="E820" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="D821" t="n">
+        <v>16294565</v>
+      </c>
+      <c r="E821" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>159.3</v>
+      </c>
+      <c r="D822" t="n">
+        <v>9746155</v>
+      </c>
+      <c r="E822" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G822"/>
+  <dimension ref="A1:G828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22544,6 +22544,168 @@
         </is>
       </c>
     </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="D823" t="n">
+        <v>155626055</v>
+      </c>
+      <c r="E823" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="D824" t="n">
+        <v>126020027</v>
+      </c>
+      <c r="E824" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>441</v>
+      </c>
+      <c r="D825" t="n">
+        <v>22310493</v>
+      </c>
+      <c r="E825" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="D826" t="n">
+        <v>15826218</v>
+      </c>
+      <c r="E826" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F826" t="inlineStr"/>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="D827" t="n">
+        <v>10608954</v>
+      </c>
+      <c r="E827" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="F827" t="inlineStr"/>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="D828" t="n">
+        <v>10289232</v>
+      </c>
+      <c r="E828" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F828" t="inlineStr"/>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G828"/>
+  <dimension ref="A1:G834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22706,6 +22706,168 @@
         </is>
       </c>
     </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="D829" t="n">
+        <v>118811174</v>
+      </c>
+      <c r="E829" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F829" t="inlineStr"/>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="D830" t="n">
+        <v>82395640</v>
+      </c>
+      <c r="E830" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F830" t="inlineStr"/>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="D831" t="n">
+        <v>17526084</v>
+      </c>
+      <c r="E831" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="F831" t="inlineStr"/>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>438.4</v>
+      </c>
+      <c r="D832" t="n">
+        <v>14278044</v>
+      </c>
+      <c r="E832" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F832" t="inlineStr"/>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="D833" t="n">
+        <v>13390769</v>
+      </c>
+      <c r="E833" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F833" t="inlineStr"/>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="D834" t="n">
+        <v>10702028</v>
+      </c>
+      <c r="E834" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="F834" t="inlineStr"/>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G834"/>
+  <dimension ref="A1:G840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22868,6 +22868,168 @@
         </is>
       </c>
     </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D835" t="n">
+        <v>109459957</v>
+      </c>
+      <c r="E835" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F835" t="inlineStr"/>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D836" t="n">
+        <v>78361085</v>
+      </c>
+      <c r="E836" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="F836" t="inlineStr"/>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="D837" t="n">
+        <v>17491240</v>
+      </c>
+      <c r="E837" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F837" t="inlineStr"/>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="D838" t="n">
+        <v>15461313</v>
+      </c>
+      <c r="E838" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="F838" t="inlineStr"/>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>436.6</v>
+      </c>
+      <c r="D839" t="n">
+        <v>9114446</v>
+      </c>
+      <c r="E839" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="F839" t="inlineStr"/>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="D840" t="n">
+        <v>6590612</v>
+      </c>
+      <c r="E840" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F840" t="inlineStr"/>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G840"/>
+  <dimension ref="A1:G846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23030,6 +23030,168 @@
         </is>
       </c>
     </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D841" t="n">
+        <v>109449957</v>
+      </c>
+      <c r="E841" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F841" t="inlineStr"/>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D842" t="n">
+        <v>78353485</v>
+      </c>
+      <c r="E842" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="F842" t="inlineStr"/>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="D843" t="n">
+        <v>17491240</v>
+      </c>
+      <c r="E843" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F843" t="inlineStr"/>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="D844" t="n">
+        <v>15449813</v>
+      </c>
+      <c r="E844" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="F844" t="inlineStr"/>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>436.6</v>
+      </c>
+      <c r="D845" t="n">
+        <v>9113746</v>
+      </c>
+      <c r="E845" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="F845" t="inlineStr"/>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="D846" t="n">
+        <v>6560612</v>
+      </c>
+      <c r="E846" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F846" t="inlineStr"/>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G846"/>
+  <dimension ref="A1:G852"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23192,6 +23192,168 @@
         </is>
       </c>
     </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D847" t="n">
+        <v>109449957</v>
+      </c>
+      <c r="E847" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F847" t="inlineStr"/>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D848" t="n">
+        <v>78353485</v>
+      </c>
+      <c r="E848" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="F848" t="inlineStr"/>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="D849" t="n">
+        <v>17491240</v>
+      </c>
+      <c r="E849" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F849" t="inlineStr"/>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="D850" t="n">
+        <v>15449813</v>
+      </c>
+      <c r="E850" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="F850" t="inlineStr"/>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>436.6</v>
+      </c>
+      <c r="D851" t="n">
+        <v>9113746</v>
+      </c>
+      <c r="E851" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="F851" t="inlineStr"/>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="D852" t="n">
+        <v>6560612</v>
+      </c>
+      <c r="E852" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F852" t="inlineStr"/>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G852"/>
+  <dimension ref="A1:G858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23354,6 +23354,144 @@
         </is>
       </c>
     </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr"/>
+      <c r="D853" t="n">
+        <v>172750357</v>
+      </c>
+      <c r="E853" t="inlineStr"/>
+      <c r="F853" t="inlineStr"/>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr"/>
+      <c r="D854" t="n">
+        <v>110319422</v>
+      </c>
+      <c r="E854" t="inlineStr"/>
+      <c r="F854" t="inlineStr"/>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr"/>
+      <c r="D855" t="n">
+        <v>16902950</v>
+      </c>
+      <c r="E855" t="inlineStr"/>
+      <c r="F855" t="inlineStr"/>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr"/>
+      <c r="D856" t="n">
+        <v>15335650</v>
+      </c>
+      <c r="E856" t="inlineStr"/>
+      <c r="F856" t="inlineStr"/>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr"/>
+      <c r="D857" t="n">
+        <v>14741662</v>
+      </c>
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr"/>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr"/>
+      <c r="D858" t="n">
+        <v>12829024</v>
+      </c>
+      <c r="E858" t="inlineStr"/>
+      <c r="F858" t="inlineStr"/>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G858"/>
+  <dimension ref="A1:G864"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23492,6 +23492,144 @@
         </is>
       </c>
     </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr"/>
+      <c r="D859" t="n">
+        <v>263172891</v>
+      </c>
+      <c r="E859" t="inlineStr"/>
+      <c r="F859" t="inlineStr"/>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr"/>
+      <c r="D860" t="n">
+        <v>146238749</v>
+      </c>
+      <c r="E860" t="inlineStr"/>
+      <c r="F860" t="inlineStr"/>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr"/>
+      <c r="D861" t="n">
+        <v>33623155</v>
+      </c>
+      <c r="E861" t="inlineStr"/>
+      <c r="F861" t="inlineStr"/>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr"/>
+      <c r="D862" t="n">
+        <v>28707971</v>
+      </c>
+      <c r="E862" t="inlineStr"/>
+      <c r="F862" t="inlineStr"/>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr"/>
+      <c r="D863" t="n">
+        <v>18016336</v>
+      </c>
+      <c r="E863" t="inlineStr"/>
+      <c r="F863" t="inlineStr"/>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr"/>
+      <c r="D864" t="n">
+        <v>10739154</v>
+      </c>
+      <c r="E864" t="inlineStr"/>
+      <c r="F864" t="inlineStr"/>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G864"/>
+  <dimension ref="A1:G870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23630,6 +23630,144 @@
         </is>
       </c>
     </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr"/>
+      <c r="D865" t="n">
+        <v>232983384</v>
+      </c>
+      <c r="E865" t="inlineStr"/>
+      <c r="F865" t="inlineStr"/>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr"/>
+      <c r="D866" t="n">
+        <v>120223400</v>
+      </c>
+      <c r="E866" t="inlineStr"/>
+      <c r="F866" t="inlineStr"/>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr"/>
+      <c r="D867" t="n">
+        <v>31984827</v>
+      </c>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr"/>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr"/>
+      <c r="D868" t="n">
+        <v>22637603</v>
+      </c>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr"/>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr"/>
+      <c r="D869" t="n">
+        <v>18982984</v>
+      </c>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr"/>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr"/>
+      <c r="D870" t="n">
+        <v>7997912</v>
+      </c>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr"/>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G870"/>
+  <dimension ref="A1:G876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23768,6 +23768,168 @@
         </is>
       </c>
     </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="D871" t="n">
+        <v>232919384</v>
+      </c>
+      <c r="E871" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F871" t="inlineStr"/>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="D872" t="n">
+        <v>120214000</v>
+      </c>
+      <c r="E872" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F872" t="inlineStr"/>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="D873" t="n">
+        <v>31983827</v>
+      </c>
+      <c r="E873" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F873" t="inlineStr"/>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>431</v>
+      </c>
+      <c r="D874" t="n">
+        <v>22634903</v>
+      </c>
+      <c r="E874" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F874" t="inlineStr"/>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="D875" t="n">
+        <v>18982584</v>
+      </c>
+      <c r="E875" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F875" t="inlineStr"/>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>158</v>
+      </c>
+      <c r="D876" t="n">
+        <v>7997112</v>
+      </c>
+      <c r="E876" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="F876" t="inlineStr"/>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G876"/>
+  <dimension ref="A1:G882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23930,6 +23930,144 @@
         </is>
       </c>
     </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr"/>
+      <c r="D877" t="n">
+        <v>172060384</v>
+      </c>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr"/>
+      <c r="D878" t="n">
+        <v>129404051</v>
+      </c>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr"/>
+      <c r="D879" t="n">
+        <v>24969574</v>
+      </c>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr"/>
+      <c r="D880" t="n">
+        <v>22488555</v>
+      </c>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr"/>
+      <c r="D881" t="n">
+        <v>19108745</v>
+      </c>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr"/>
+      <c r="D882" t="n">
+        <v>15539618</v>
+      </c>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G882"/>
+  <dimension ref="A1:G888"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24068,6 +24068,168 @@
         </is>
       </c>
     </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="D883" t="n">
+        <v>171972384</v>
+      </c>
+      <c r="E883" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F883" t="inlineStr"/>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="D884" t="n">
+        <v>129403051</v>
+      </c>
+      <c r="E884" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="D885" t="n">
+        <v>24964374</v>
+      </c>
+      <c r="E885" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="F885" t="inlineStr"/>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="D886" t="n">
+        <v>22485255</v>
+      </c>
+      <c r="E886" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="D887" t="n">
+        <v>19108045</v>
+      </c>
+      <c r="E887" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="D888" t="n">
+        <v>15537318</v>
+      </c>
+      <c r="E888" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G888"/>
+  <dimension ref="A1:G894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24230,6 +24230,168 @@
         </is>
       </c>
     </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="D889" t="n">
+        <v>171972384</v>
+      </c>
+      <c r="E889" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F889" t="inlineStr"/>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="D890" t="n">
+        <v>129403051</v>
+      </c>
+      <c r="E890" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="F890" t="inlineStr"/>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="D891" t="n">
+        <v>24964374</v>
+      </c>
+      <c r="E891" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="D892" t="n">
+        <v>22485255</v>
+      </c>
+      <c r="E892" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="D893" t="n">
+        <v>19108045</v>
+      </c>
+      <c r="E893" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="D894" t="n">
+        <v>15537318</v>
+      </c>
+      <c r="E894" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F894" t="inlineStr"/>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G894"/>
+  <dimension ref="A1:G900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24392,6 +24392,168 @@
         </is>
       </c>
     </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="D895" t="n">
+        <v>88394509</v>
+      </c>
+      <c r="E895" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="F895" t="inlineStr"/>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="D896" t="n">
+        <v>70339180</v>
+      </c>
+      <c r="E896" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="F896" t="inlineStr"/>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="D897" t="n">
+        <v>16338919</v>
+      </c>
+      <c r="E897" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F897" t="inlineStr"/>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="D898" t="n">
+        <v>11889096</v>
+      </c>
+      <c r="E898" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F898" t="inlineStr"/>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="D899" t="n">
+        <v>9860715</v>
+      </c>
+      <c r="E899" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F899" t="inlineStr"/>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>423</v>
+      </c>
+      <c r="D900" t="n">
+        <v>8709438</v>
+      </c>
+      <c r="E900" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F900" t="inlineStr"/>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G900"/>
+  <dimension ref="A1:G906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24554,6 +24554,144 @@
         </is>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr"/>
+      <c r="D901" t="n">
+        <v>98690629</v>
+      </c>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr"/>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr"/>
+      <c r="D902" t="n">
+        <v>81203405</v>
+      </c>
+      <c r="E902" t="inlineStr"/>
+      <c r="F902" t="inlineStr"/>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr"/>
+      <c r="D903" t="n">
+        <v>10051007</v>
+      </c>
+      <c r="E903" t="inlineStr"/>
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr"/>
+      <c r="D904" t="n">
+        <v>10030081</v>
+      </c>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr"/>
+      <c r="D905" t="n">
+        <v>9900789</v>
+      </c>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr"/>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr"/>
+      <c r="D906" t="n">
+        <v>8140224</v>
+      </c>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr"/>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G906"/>
+  <dimension ref="A1:G912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24692,6 +24692,144 @@
         </is>
       </c>
     </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr"/>
+      <c r="D907" t="n">
+        <v>63054733</v>
+      </c>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr"/>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr"/>
+      <c r="D908" t="n">
+        <v>46116080</v>
+      </c>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr"/>
+      <c r="D909" t="n">
+        <v>12441640</v>
+      </c>
+      <c r="E909" t="inlineStr"/>
+      <c r="F909" t="inlineStr"/>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr"/>
+      <c r="D910" t="n">
+        <v>11286030</v>
+      </c>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr"/>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr"/>
+      <c r="D911" t="n">
+        <v>6298957</v>
+      </c>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr"/>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr"/>
+      <c r="D912" t="n">
+        <v>6125452</v>
+      </c>
+      <c r="E912" t="inlineStr"/>
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G912"/>
+  <dimension ref="A1:G918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24830,6 +24830,144 @@
         </is>
       </c>
     </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr"/>
+      <c r="D913" t="n">
+        <v>224165410</v>
+      </c>
+      <c r="E913" t="inlineStr"/>
+      <c r="F913" t="inlineStr"/>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr"/>
+      <c r="D914" t="n">
+        <v>97457849</v>
+      </c>
+      <c r="E914" t="inlineStr"/>
+      <c r="F914" t="inlineStr"/>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr"/>
+      <c r="D915" t="n">
+        <v>32302844</v>
+      </c>
+      <c r="E915" t="inlineStr"/>
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr"/>
+      <c r="D916" t="n">
+        <v>30206975</v>
+      </c>
+      <c r="E916" t="inlineStr"/>
+      <c r="F916" t="inlineStr"/>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr"/>
+      <c r="D917" t="n">
+        <v>22588514</v>
+      </c>
+      <c r="E917" t="inlineStr"/>
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr"/>
+      <c r="D918" t="n">
+        <v>18847625</v>
+      </c>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr"/>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G918"/>
+  <dimension ref="A1:G924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24968,6 +24968,144 @@
         </is>
       </c>
     </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr"/>
+      <c r="D919" t="n">
+        <v>255626451</v>
+      </c>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="inlineStr"/>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr"/>
+      <c r="D920" t="n">
+        <v>170033285</v>
+      </c>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr"/>
+      <c r="D921" t="n">
+        <v>23935883</v>
+      </c>
+      <c r="E921" t="inlineStr"/>
+      <c r="F921" t="inlineStr"/>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr"/>
+      <c r="D922" t="n">
+        <v>20420700</v>
+      </c>
+      <c r="E922" t="inlineStr"/>
+      <c r="F922" t="inlineStr"/>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr"/>
+      <c r="D923" t="n">
+        <v>20033846</v>
+      </c>
+      <c r="E923" t="inlineStr"/>
+      <c r="F923" t="inlineStr"/>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr"/>
+      <c r="D924" t="n">
+        <v>15671487</v>
+      </c>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G924"/>
+  <dimension ref="A1:G930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25106,6 +25106,184 @@
         </is>
       </c>
     </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="D925" t="n">
+        <v>255608451</v>
+      </c>
+      <c r="E925" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="D926" t="n">
+        <v>172126285</v>
+      </c>
+      <c r="E926" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F926" t="inlineStr"/>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="D927" t="n">
+        <v>23926883</v>
+      </c>
+      <c r="E927" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>424.8</v>
+      </c>
+      <c r="D928" t="n">
+        <v>20422500</v>
+      </c>
+      <c r="E928" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="D929" t="n">
+        <v>20054046</v>
+      </c>
+      <c r="E929" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="D930" t="n">
+        <v>15711887</v>
+      </c>
+      <c r="E930" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F930" t="inlineStr"/>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G930"/>
+  <dimension ref="A1:G936"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25284,6 +25284,184 @@
         </is>
       </c>
     </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="D931" t="n">
+        <v>255608451</v>
+      </c>
+      <c r="E931" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="D932" t="n">
+        <v>172126285</v>
+      </c>
+      <c r="E932" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="D933" t="n">
+        <v>23926883</v>
+      </c>
+      <c r="E933" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>424.8</v>
+      </c>
+      <c r="D934" t="n">
+        <v>20422500</v>
+      </c>
+      <c r="E934" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="D935" t="n">
+        <v>20054046</v>
+      </c>
+      <c r="E935" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="D936" t="n">
+        <v>15711887</v>
+      </c>
+      <c r="E936" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F936" t="inlineStr"/>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G936"/>
+  <dimension ref="A1:G942"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25462,6 +25462,144 @@
         </is>
       </c>
     </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr"/>
+      <c r="D937" t="n">
+        <v>182808010</v>
+      </c>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr"/>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr"/>
+      <c r="D938" t="n">
+        <v>149150984</v>
+      </c>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr"/>
+      <c r="D939" t="n">
+        <v>24461551</v>
+      </c>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr"/>
+      <c r="D940" t="n">
+        <v>14011838</v>
+      </c>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="inlineStr"/>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr"/>
+      <c r="D941" t="n">
+        <v>13773062</v>
+      </c>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr"/>
+      <c r="D942" t="n">
+        <v>9526825</v>
+      </c>
+      <c r="E942" t="inlineStr"/>
+      <c r="F942" t="inlineStr"/>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G942"/>
+  <dimension ref="A1:G948"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25600,6 +25600,144 @@
         </is>
       </c>
     </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr"/>
+      <c r="D943" t="n">
+        <v>168953993</v>
+      </c>
+      <c r="E943" t="inlineStr"/>
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr"/>
+      <c r="D944" t="n">
+        <v>154848800</v>
+      </c>
+      <c r="E944" t="inlineStr"/>
+      <c r="F944" t="inlineStr"/>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr"/>
+      <c r="D945" t="n">
+        <v>21338036</v>
+      </c>
+      <c r="E945" t="inlineStr"/>
+      <c r="F945" t="inlineStr"/>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr"/>
+      <c r="D946" t="n">
+        <v>18242862</v>
+      </c>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="inlineStr"/>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr"/>
+      <c r="D947" t="n">
+        <v>12775121</v>
+      </c>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr"/>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr"/>
+      <c r="D948" t="n">
+        <v>12729135</v>
+      </c>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="inlineStr"/>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G948"/>
+  <dimension ref="A1:G954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25738,6 +25738,176 @@
         </is>
       </c>
     </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="D949" t="n">
+        <v>277521609</v>
+      </c>
+      <c r="E949" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="D950" t="n">
+        <v>187557436</v>
+      </c>
+      <c r="E950" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="F950" t="inlineStr"/>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="D951" t="n">
+        <v>65472806</v>
+      </c>
+      <c r="E951" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>423.4</v>
+      </c>
+      <c r="D952" t="n">
+        <v>19933648</v>
+      </c>
+      <c r="E952" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="F952" t="inlineStr"/>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="D953" t="n">
+        <v>15055021</v>
+      </c>
+      <c r="E953" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="F953" t="inlineStr"/>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>148</v>
+      </c>
+      <c r="D954" t="n">
+        <v>7389913</v>
+      </c>
+      <c r="E954" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="F954" t="inlineStr"/>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G954"/>
+  <dimension ref="A1:G960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25908,6 +25908,168 @@
         </is>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="D955" t="n">
+        <v>266495588</v>
+      </c>
+      <c r="E955" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F955" t="inlineStr"/>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="D956" t="n">
+        <v>226410981</v>
+      </c>
+      <c r="E956" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F956" t="inlineStr"/>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="D957" t="n">
+        <v>33700990</v>
+      </c>
+      <c r="E957" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="F957" t="inlineStr"/>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="D958" t="n">
+        <v>20660817</v>
+      </c>
+      <c r="E958" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="F958" t="inlineStr"/>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="D959" t="n">
+        <v>16039825</v>
+      </c>
+      <c r="E959" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F959" t="inlineStr"/>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="D960" t="n">
+        <v>10134643</v>
+      </c>
+      <c r="E960" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F960" t="inlineStr"/>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G960"/>
+  <dimension ref="A1:G966"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26070,6 +26070,168 @@
         </is>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="D961" t="n">
+        <v>182667483</v>
+      </c>
+      <c r="E961" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F961" t="inlineStr"/>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="D962" t="n">
+        <v>154063468</v>
+      </c>
+      <c r="E962" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F962" t="inlineStr"/>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="D963" t="n">
+        <v>22668265</v>
+      </c>
+      <c r="E963" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F963" t="inlineStr"/>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="D964" t="n">
+        <v>18749869</v>
+      </c>
+      <c r="E964" t="n">
+        <v>0</v>
+      </c>
+      <c r="F964" t="inlineStr"/>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="D965" t="n">
+        <v>12782058</v>
+      </c>
+      <c r="E965" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F965" t="inlineStr"/>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="D966" t="n">
+        <v>12156298</v>
+      </c>
+      <c r="E966" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F966" t="inlineStr"/>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G966"/>
+  <dimension ref="A1:G972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26232,6 +26232,168 @@
         </is>
       </c>
     </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="D967" t="n">
+        <v>183102483</v>
+      </c>
+      <c r="E967" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F967" t="inlineStr"/>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="D968" t="n">
+        <v>154063268</v>
+      </c>
+      <c r="E968" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F968" t="inlineStr"/>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="D969" t="n">
+        <v>22655665</v>
+      </c>
+      <c r="E969" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F969" t="inlineStr"/>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="D970" t="n">
+        <v>18752869</v>
+      </c>
+      <c r="E970" t="n">
+        <v>0</v>
+      </c>
+      <c r="F970" t="inlineStr"/>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="D971" t="n">
+        <v>12817758</v>
+      </c>
+      <c r="E971" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F971" t="inlineStr"/>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="D972" t="n">
+        <v>12339898</v>
+      </c>
+      <c r="E972" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F972" t="inlineStr"/>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G972"/>
+  <dimension ref="A1:G978"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26394,6 +26394,168 @@
         </is>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="D973" t="n">
+        <v>183102483</v>
+      </c>
+      <c r="E973" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F973" t="inlineStr"/>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="D974" t="n">
+        <v>154063268</v>
+      </c>
+      <c r="E974" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F974" t="inlineStr"/>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="D975" t="n">
+        <v>22655665</v>
+      </c>
+      <c r="E975" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F975" t="inlineStr"/>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="D976" t="n">
+        <v>18752869</v>
+      </c>
+      <c r="E976" t="n">
+        <v>0</v>
+      </c>
+      <c r="F976" t="inlineStr"/>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="D977" t="n">
+        <v>12817758</v>
+      </c>
+      <c r="E977" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F977" t="inlineStr"/>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="D978" t="n">
+        <v>12339898</v>
+      </c>
+      <c r="E978" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F978" t="inlineStr"/>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G978"/>
+  <dimension ref="A1:G984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26556,6 +26556,168 @@
         </is>
       </c>
     </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="D979" t="n">
+        <v>183102483</v>
+      </c>
+      <c r="E979" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F979" t="inlineStr"/>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="D980" t="n">
+        <v>154063268</v>
+      </c>
+      <c r="E980" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F980" t="inlineStr"/>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="D981" t="n">
+        <v>22655665</v>
+      </c>
+      <c r="E981" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F981" t="inlineStr"/>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="D982" t="n">
+        <v>18752869</v>
+      </c>
+      <c r="E982" t="n">
+        <v>0</v>
+      </c>
+      <c r="F982" t="inlineStr"/>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="D983" t="n">
+        <v>12817758</v>
+      </c>
+      <c r="E983" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F983" t="inlineStr"/>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="D984" t="n">
+        <v>12339898</v>
+      </c>
+      <c r="E984" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F984" t="inlineStr"/>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G984"/>
+  <dimension ref="A1:G990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26718,6 +26718,168 @@
         </is>
       </c>
     </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="D985" t="n">
+        <v>159435945</v>
+      </c>
+      <c r="E985" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F985" t="inlineStr"/>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="D986" t="n">
+        <v>106056819</v>
+      </c>
+      <c r="E986" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F986" t="inlineStr"/>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="D987" t="n">
+        <v>23683952</v>
+      </c>
+      <c r="E987" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F987" t="inlineStr"/>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>410.4</v>
+      </c>
+      <c r="D988" t="n">
+        <v>22820913</v>
+      </c>
+      <c r="E988" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="F988" t="inlineStr"/>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="D989" t="n">
+        <v>13990598</v>
+      </c>
+      <c r="E989" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="F989" t="inlineStr"/>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="D990" t="n">
+        <v>13626766</v>
+      </c>
+      <c r="E990" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F990" t="inlineStr"/>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G990"/>
+  <dimension ref="A1:G996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26880,6 +26880,168 @@
         </is>
       </c>
     </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="D991" t="n">
+        <v>146759276</v>
+      </c>
+      <c r="E991" t="n">
+        <v>0</v>
+      </c>
+      <c r="F991" t="inlineStr"/>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D992" t="n">
+        <v>144467851</v>
+      </c>
+      <c r="E992" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="F992" t="inlineStr"/>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="D993" t="n">
+        <v>37783935</v>
+      </c>
+      <c r="E993" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="F993" t="inlineStr"/>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="D994" t="n">
+        <v>20550985</v>
+      </c>
+      <c r="E994" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="F994" t="inlineStr"/>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="D995" t="n">
+        <v>19481840</v>
+      </c>
+      <c r="E995" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="F995" t="inlineStr"/>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="D996" t="n">
+        <v>5470795</v>
+      </c>
+      <c r="E996" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F996" t="inlineStr"/>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G996"/>
+  <dimension ref="A1:G1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27042,6 +27042,168 @@
         </is>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D997" t="n">
+        <v>265447170</v>
+      </c>
+      <c r="E997" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="F997" t="inlineStr"/>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D998" t="n">
+        <v>149479760</v>
+      </c>
+      <c r="E998" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="F998" t="inlineStr"/>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="D999" t="n">
+        <v>60746647</v>
+      </c>
+      <c r="E999" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="F999" t="inlineStr"/>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>37843088</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="F1000" t="inlineStr"/>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>35128666</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="F1001" t="inlineStr"/>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>10622221</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="F1002" t="inlineStr"/>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1002"/>
+  <dimension ref="A1:G1008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27204,6 +27204,176 @@
         </is>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>412306503</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1003" t="inlineStr"/>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>216291102</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>51639425</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>386</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>33142473</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1006" t="inlineStr"/>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>30566200</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1007" t="inlineStr"/>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>11995864</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F1008" t="inlineStr"/>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1008"/>
+  <dimension ref="A1:G1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27374,6 +27374,176 @@
         </is>
       </c>
     </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>412299503</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1009" t="inlineStr"/>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>216285102</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>51810625</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>386</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>33161473</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1012" t="inlineStr"/>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>30564900</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1013" t="inlineStr"/>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>12090264</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F1014" t="inlineStr"/>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1014"/>
+  <dimension ref="A1:G1020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27544,6 +27544,176 @@
         </is>
       </c>
     </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>412299503</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1015" t="inlineStr"/>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>216285102</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>51810625</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>386</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>33161473</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1018" t="inlineStr"/>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>30564900</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1019" t="inlineStr"/>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>12090264</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F1020" t="inlineStr"/>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1020"/>
+  <dimension ref="A1:G1026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27714,6 +27714,144 @@
         </is>
       </c>
     </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr"/>
+      <c r="D1021" t="n">
+        <v>198560002</v>
+      </c>
+      <c r="E1021" t="inlineStr"/>
+      <c r="F1021" t="inlineStr"/>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr"/>
+      <c r="D1022" t="n">
+        <v>93023145</v>
+      </c>
+      <c r="E1022" t="inlineStr"/>
+      <c r="F1022" t="inlineStr"/>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr"/>
+      <c r="D1023" t="n">
+        <v>37179856</v>
+      </c>
+      <c r="E1023" t="inlineStr"/>
+      <c r="F1023" t="inlineStr"/>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr"/>
+      <c r="D1024" t="n">
+        <v>18430441</v>
+      </c>
+      <c r="E1024" t="inlineStr"/>
+      <c r="F1024" t="inlineStr"/>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr"/>
+      <c r="D1025" t="n">
+        <v>16943609</v>
+      </c>
+      <c r="E1025" t="inlineStr"/>
+      <c r="F1025" t="inlineStr"/>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr"/>
+      <c r="D1026" t="n">
+        <v>11151564</v>
+      </c>
+      <c r="E1026" t="inlineStr"/>
+      <c r="F1026" t="inlineStr"/>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1026"/>
+  <dimension ref="A1:G1032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27852,6 +27852,168 @@
         </is>
       </c>
     </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>264849822</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F1027" t="inlineStr"/>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>138340888</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="F1028" t="inlineStr"/>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>36513272</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="F1029" t="inlineStr"/>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>21809697</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>16238414</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F1031" t="inlineStr"/>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>15914527</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1032"/>
+  <dimension ref="A1:G1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28014,6 +28014,144 @@
         </is>
       </c>
     </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr"/>
+      <c r="D1033" t="n">
+        <v>179382541</v>
+      </c>
+      <c r="E1033" t="inlineStr"/>
+      <c r="F1033" t="inlineStr"/>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr"/>
+      <c r="D1034" t="n">
+        <v>76649974</v>
+      </c>
+      <c r="E1034" t="inlineStr"/>
+      <c r="F1034" t="inlineStr"/>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr"/>
+      <c r="D1035" t="n">
+        <v>23325345</v>
+      </c>
+      <c r="E1035" t="inlineStr"/>
+      <c r="F1035" t="inlineStr"/>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr"/>
+      <c r="D1036" t="n">
+        <v>18651098</v>
+      </c>
+      <c r="E1036" t="inlineStr"/>
+      <c r="F1036" t="inlineStr"/>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr"/>
+      <c r="D1037" t="n">
+        <v>13705006</v>
+      </c>
+      <c r="E1037" t="inlineStr"/>
+      <c r="F1037" t="inlineStr"/>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr"/>
+      <c r="D1038" t="n">
+        <v>13585186</v>
+      </c>
+      <c r="E1038" t="inlineStr"/>
+      <c r="F1038" t="inlineStr"/>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1038"/>
+  <dimension ref="A1:G1044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28152,6 +28152,144 @@
         </is>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr"/>
+      <c r="D1039" t="n">
+        <v>316260623</v>
+      </c>
+      <c r="E1039" t="inlineStr"/>
+      <c r="F1039" t="inlineStr"/>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr"/>
+      <c r="D1040" t="n">
+        <v>88051677</v>
+      </c>
+      <c r="E1040" t="inlineStr"/>
+      <c r="F1040" t="inlineStr"/>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr"/>
+      <c r="D1041" t="n">
+        <v>27175118</v>
+      </c>
+      <c r="E1041" t="inlineStr"/>
+      <c r="F1041" t="inlineStr"/>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr"/>
+      <c r="D1042" t="n">
+        <v>21268279</v>
+      </c>
+      <c r="E1042" t="inlineStr"/>
+      <c r="F1042" t="inlineStr"/>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr"/>
+      <c r="D1043" t="n">
+        <v>20994465</v>
+      </c>
+      <c r="E1043" t="inlineStr"/>
+      <c r="F1043" t="inlineStr"/>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr"/>
+      <c r="D1044" t="n">
+        <v>9668716</v>
+      </c>
+      <c r="E1044" t="inlineStr"/>
+      <c r="F1044" t="inlineStr"/>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1044"/>
+  <dimension ref="A1:G1050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28290,6 +28290,144 @@
         </is>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr"/>
+      <c r="D1045" t="n">
+        <v>281495562</v>
+      </c>
+      <c r="E1045" t="inlineStr"/>
+      <c r="F1045" t="inlineStr"/>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>1810.HK</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr"/>
+      <c r="D1046" t="n">
+        <v>207860564</v>
+      </c>
+      <c r="E1046" t="inlineStr"/>
+      <c r="F1046" t="inlineStr"/>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>1211.HK</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr"/>
+      <c r="D1047" t="n">
+        <v>36602423</v>
+      </c>
+      <c r="E1047" t="inlineStr"/>
+      <c r="F1047" t="inlineStr"/>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>3690.HK</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr"/>
+      <c r="D1048" t="n">
+        <v>36190642</v>
+      </c>
+      <c r="E1048" t="inlineStr"/>
+      <c r="F1048" t="inlineStr"/>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr"/>
+      <c r="D1049" t="n">
+        <v>22275554</v>
+      </c>
+      <c r="E1049" t="inlineStr"/>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr"/>
+      <c r="D1050" t="n">
+        <v>10700902</v>
+      </c>
+      <c r="E1050" t="inlineStr"/>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
